--- a/Budgetplanung.xlsx
+++ b/Budgetplanung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\factory_in_a_box\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EF3F64-C5CE-45EE-A2B9-7FC272806C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CB7409-D8CA-4D08-AD82-B289F3FD1B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{8C9A7E15-76E0-4799-BA50-96435E031197}"/>
+    <workbookView xWindow="3800" yWindow="3800" windowWidth="28800" windowHeight="15370" xr2:uid="{8C9A7E15-76E0-4799-BA50-96435E031197}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Bauteil</t>
   </si>
@@ -53,12 +53,6 @@
     <t>Sortierer</t>
   </si>
   <si>
-    <t>Radxa Zero mit Cam</t>
-  </si>
-  <si>
-    <t>Platine</t>
-  </si>
-  <si>
     <t>Aluprofile</t>
   </si>
   <si>
@@ -77,9 +71,6 @@
     <t>Zylinder</t>
   </si>
   <si>
-    <t>Ventil</t>
-  </si>
-  <si>
     <t>Schlauch</t>
   </si>
   <si>
@@ -93,6 +84,21 @@
   </si>
   <si>
     <t>Preis</t>
+  </si>
+  <si>
+    <t>Factory Control Board</t>
+  </si>
+  <si>
+    <t>Vakuumpumpe</t>
+  </si>
+  <si>
+    <t>Ventile</t>
+  </si>
+  <si>
+    <t>Kleinteilepauschale</t>
+  </si>
+  <si>
+    <t>Stecker Buchsen für FCB</t>
   </si>
 </sst>
 </file>
@@ -464,29 +470,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C796F5E-DCF3-4B60-90D7-1A4C9D15602F}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.86328125" customWidth="1"/>
+    <col min="1" max="1" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -494,7 +500,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -502,7 +508,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -510,108 +516,124 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B7">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>10</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>13</v>
       </c>
       <c r="B14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
